--- a/ТАРИФЫ РК ТАБЛИЦА.xlsx
+++ b/ТАРИФЫ РК ТАБЛИЦА.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stanislavhvostov/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49752AAE-2B12-1B45-95A5-D8CB7CA17993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232C4FC2-3123-E84D-8522-44CDF2B353B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="580" windowWidth="27040" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1373,9 +1373,7 @@
         <v>48800</v>
       </c>
       <c r="G6" s="14"/>
-      <c r="H6" s="14">
-        <v>65000</v>
-      </c>
+      <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="J6" s="14">
         <v>56500</v>
@@ -1389,7 +1387,7 @@
       <c r="M6" s="14"/>
       <c r="N6" s="45">
         <f t="shared" ref="N6:N22" si="0">AVERAGE(B6:M6)</f>
-        <v>59383.333333333336</v>
+        <v>58260</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>6</v>
@@ -1413,9 +1411,7 @@
         <v>57950</v>
       </c>
       <c r="G7" s="14"/>
-      <c r="H7" s="14">
-        <v>70000</v>
-      </c>
+      <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="14">
         <v>65000</v>
@@ -1429,7 +1425,7 @@
       <c r="M7" s="14"/>
       <c r="N7" s="45">
         <f t="shared" si="0"/>
-        <v>67991.666666666672</v>
+        <v>67590</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>7</v>
@@ -1499,9 +1495,7 @@
       <c r="G9" s="14">
         <v>118320</v>
       </c>
-      <c r="H9" s="14">
-        <v>128000</v>
-      </c>
+      <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="14">
         <v>133800</v>
@@ -1517,7 +1511,7 @@
       </c>
       <c r="N9" s="45">
         <f t="shared" si="0"/>
-        <v>137733.70000000001</v>
+        <v>138815.22222222222</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>9</v>
@@ -1581,9 +1575,7 @@
         <v>177917</v>
       </c>
       <c r="G11" s="14"/>
-      <c r="H11" s="14">
-        <v>175000</v>
-      </c>
+      <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14">
         <v>180000</v>
@@ -1599,7 +1591,7 @@
       </c>
       <c r="N11" s="45">
         <f t="shared" si="0"/>
-        <v>205613</v>
+        <v>209439.625</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>11</v>
@@ -3665,18 +3657,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8 J8 F8 H8">
-    <cfRule type="colorScale" priority="329">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D8">
     <cfRule type="colorScale" priority="347">
       <colorScale>
@@ -3725,6 +3705,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D12 J12 F12 H12">
+    <cfRule type="colorScale" priority="325">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D12">
     <cfRule type="colorScale" priority="343">
       <colorScale>
@@ -3749,18 +3741,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D14 J14 F14 H14">
-    <cfRule type="colorScale" priority="323">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D14">
     <cfRule type="colorScale" priority="341">
       <colorScale>
@@ -3785,18 +3765,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D16 J16 F16 H16">
-    <cfRule type="colorScale" priority="321">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D16">
     <cfRule type="colorScale" priority="339">
       <colorScale>
@@ -3845,18 +3813,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D22 J22 F22 H22">
-    <cfRule type="colorScale" priority="315">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D22">
     <cfRule type="colorScale" priority="333">
       <colorScale>
@@ -3917,68 +3873,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5 J5 D5 H5">
-    <cfRule type="colorScale" priority="332">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6 J6 D6 H6">
-    <cfRule type="colorScale" priority="331">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7 J7 D7 H7">
-    <cfRule type="colorScale" priority="330">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9 J9 D9 H9">
-    <cfRule type="colorScale" priority="328">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10 J10 D10 H10">
-    <cfRule type="colorScale" priority="327">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13 J13 D13 H13">
-    <cfRule type="colorScale" priority="324">
+  <conditionalFormatting sqref="F11 J11 D11 H11">
+    <cfRule type="colorScale" priority="326">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4397,32 +4293,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17 J17 D17 F17">
-    <cfRule type="colorScale" priority="320">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18 J18 D18:F18">
-    <cfRule type="colorScale" priority="319">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H21 J21 D21 F21">
-    <cfRule type="colorScale" priority="316">
+  <conditionalFormatting sqref="H15 J15 D15 F15">
+    <cfRule type="colorScale" priority="322">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19 J19 D19 F19">
+    <cfRule type="colorScale" priority="318">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20 J20 D20:F20">
+    <cfRule type="colorScale" priority="317">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4659,6 +4555,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J5 F5 D5 H5">
+    <cfRule type="colorScale" priority="332">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J5">
     <cfRule type="colorScale" priority="368">
       <colorScale>
@@ -4671,6 +4579,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J6 F6 D6 H6">
+    <cfRule type="colorScale" priority="331">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J6">
     <cfRule type="colorScale" priority="367">
       <colorScale>
@@ -4683,6 +4603,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J7 F7 D7 H7">
+    <cfRule type="colorScale" priority="330">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J7">
     <cfRule type="colorScale" priority="366">
       <colorScale>
@@ -4695,6 +4627,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J8 D8 F8 H8">
+    <cfRule type="colorScale" priority="329">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J8">
     <cfRule type="colorScale" priority="365">
       <colorScale>
@@ -4707,6 +4651,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J9 F9 D9 H9">
+    <cfRule type="colorScale" priority="328">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J9">
     <cfRule type="colorScale" priority="364">
       <colorScale>
@@ -4719,6 +4675,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J10 F10 D10 H10">
+    <cfRule type="colorScale" priority="327">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J10">
     <cfRule type="colorScale" priority="363">
       <colorScale>
@@ -4731,18 +4699,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11 F11 D11 H11">
-    <cfRule type="colorScale" priority="326">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J11">
     <cfRule type="colorScale" priority="362">
       <colorScale>
@@ -4755,18 +4711,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J12 D12 F12 H12">
-    <cfRule type="colorScale" priority="325">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J12">
     <cfRule type="colorScale" priority="361">
       <colorScale>
@@ -4779,6 +4723,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J13 F13 D13 H13">
+    <cfRule type="colorScale" priority="324">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J13">
     <cfRule type="colorScale" priority="360">
       <colorScale>
@@ -4791,6 +4747,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J14 D14 F14 H14">
+    <cfRule type="colorScale" priority="323">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J14">
     <cfRule type="colorScale" priority="359">
       <colorScale>
@@ -4803,18 +4771,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J15 H15 D15 F15">
-    <cfRule type="colorScale" priority="322">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J15">
     <cfRule type="colorScale" priority="358">
       <colorScale>
@@ -4827,6 +4783,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J16 D16 F16 H16">
+    <cfRule type="colorScale" priority="321">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J16">
     <cfRule type="colorScale" priority="357">
       <colorScale>
@@ -4839,6 +4807,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J17 H17 D17 F17">
+    <cfRule type="colorScale" priority="320">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J17">
     <cfRule type="colorScale" priority="356">
       <colorScale>
@@ -4851,6 +4831,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J18 H18 D18:F18">
+    <cfRule type="colorScale" priority="319">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J18">
     <cfRule type="colorScale" priority="355">
       <colorScale>
@@ -4863,18 +4855,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J19 H19 D19 F19">
-    <cfRule type="colorScale" priority="318">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J19">
     <cfRule type="colorScale" priority="354">
       <colorScale>
@@ -4887,18 +4867,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J20 H20 D20:F20">
-    <cfRule type="colorScale" priority="317">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J20">
     <cfRule type="colorScale" priority="353">
       <colorScale>
@@ -4911,8 +4879,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J21 H21 D21 F21">
+    <cfRule type="colorScale" priority="316">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J21">
     <cfRule type="colorScale" priority="352">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22 D22 F22 H22">
+    <cfRule type="colorScale" priority="315">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/ТАРИФЫ РК ТАБЛИЦА.xlsx
+++ b/ТАРИФЫ РК ТАБЛИЦА.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stanislavhvostov/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232C4FC2-3123-E84D-8522-44CDF2B353B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34541AA-D074-764D-B9C2-DF31881E480A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="27040" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="27040" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Актуальные " sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="86">
   <si>
     <t>Сияние</t>
   </si>
@@ -330,6 +330,15 @@
   </si>
   <si>
     <t xml:space="preserve">Средний </t>
+  </si>
+  <si>
+    <t>ИП Коршунов</t>
+  </si>
+  <si>
+    <t>ИП Мельник</t>
+  </si>
+  <si>
+    <t>ИП Гусманов</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +1198,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D700EC7-AC33-4A9F-90DC-87902823BDE2}">
   <sheetPr codeName="Лист2"/>
-  <dimension ref="A2:R22"/>
+  <dimension ref="A2:U22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
@@ -1201,14 +1210,14 @@
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="13.5" customWidth="1"/>
+    <col min="17" max="17" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" ht="64" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="64" x14ac:dyDescent="0.2">
       <c r="B2" s="46" t="s">
         <v>81</v>
       </c>
@@ -1227,8 +1236,11 @@
       <c r="M2" s="43" t="s">
         <v>78</v>
       </c>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
     </row>
-    <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="48" t="s">
         <v>48</v>
       </c>
@@ -1268,14 +1280,23 @@
       <c r="M3" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="N3" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="O3" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="P3" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="49"/>
       <c r="B4" s="42" t="s">
         <v>3</v>
@@ -1313,17 +1334,26 @@
       <c r="M4" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="N4" s="47" t="s">
+      <c r="N4" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -1349,17 +1379,20 @@
         <v>73000</v>
       </c>
       <c r="M5" s="14"/>
-      <c r="N5" s="45">
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="45">
         <f>AVERAGE(B5:M5)</f>
         <v>55900</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -1385,19 +1418,28 @@
         <v>77000</v>
       </c>
       <c r="M6" s="14"/>
-      <c r="N6" s="45">
-        <f t="shared" ref="N6:N22" si="0">AVERAGE(B6:M6)</f>
-        <v>58260</v>
-      </c>
-      <c r="P6" s="2" t="s">
+      <c r="N6" s="14">
+        <v>52000</v>
+      </c>
+      <c r="O6" s="14">
+        <v>52000</v>
+      </c>
+      <c r="P6" s="14">
+        <v>47000</v>
+      </c>
+      <c r="Q6" s="45">
+        <f>AVERAGE(B6:P6)</f>
+        <v>55287.5</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10">
+      <c r="T6" s="10"/>
+      <c r="U6" s="10">
         <v>58967</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1423,17 +1465,20 @@
         <v>85000</v>
       </c>
       <c r="M7" s="14"/>
-      <c r="N7" s="45">
-        <f t="shared" si="0"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="45">
+        <f t="shared" ref="Q6:Q22" si="0">AVERAGE(B7:M7)</f>
         <v>67590</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -1465,17 +1510,20 @@
         <v>133000</v>
       </c>
       <c r="M8" s="14"/>
-      <c r="N8" s="45">
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="45">
         <f t="shared" si="0"/>
         <v>104616.625</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -1509,19 +1557,22 @@
       <c r="M9" s="14">
         <v>160000</v>
       </c>
-      <c r="N9" s="45">
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="45">
         <f t="shared" si="0"/>
         <v>138815.22222222222</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="T9" s="10">
         <v>190000</v>
       </c>
-      <c r="R9" s="10"/>
+      <c r="U9" s="10"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -1547,17 +1598,20 @@
         <v>157000</v>
       </c>
       <c r="M10" s="14"/>
-      <c r="N10" s="45">
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="45">
         <f t="shared" si="0"/>
         <v>143300</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="S10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
@@ -1589,21 +1643,24 @@
       <c r="M11" s="14">
         <v>195000</v>
       </c>
-      <c r="N11" s="45">
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="45">
         <f t="shared" si="0"/>
         <v>209439.625</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="S11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="T11" s="10">
         <v>294000</v>
       </c>
-      <c r="R11" s="10">
+      <c r="U11" s="10">
         <v>198250</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -1631,19 +1688,22 @@
         <v>162000</v>
       </c>
       <c r="M12" s="14"/>
-      <c r="N12" s="45">
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="45">
         <f t="shared" si="0"/>
         <v>147325</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="S12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="T12" s="10">
         <v>190000</v>
       </c>
-      <c r="R12" s="10"/>
+      <c r="U12" s="10"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
@@ -1679,19 +1739,22 @@
       <c r="M13" s="14">
         <v>250000</v>
       </c>
-      <c r="N13" s="45">
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="45">
         <f t="shared" si="0"/>
         <v>265995</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="S13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="T13" s="10">
         <v>300000</v>
       </c>
-      <c r="R13" s="10"/>
+      <c r="U13" s="10"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1725,19 +1788,22 @@
       <c r="M14" s="14">
         <v>450000</v>
       </c>
-      <c r="N14" s="45">
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="45">
         <f t="shared" si="0"/>
         <v>442722.22222222225</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="S14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="T14" s="10">
         <v>516000</v>
       </c>
-      <c r="R14" s="10"/>
+      <c r="U14" s="10"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
@@ -1755,17 +1821,20 @@
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
       <c r="M15" s="14"/>
-      <c r="N15" s="45">
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="45">
         <f t="shared" si="0"/>
         <v>467250</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="S15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1795,19 +1864,22 @@
         <v>997000</v>
       </c>
       <c r="M16" s="14"/>
-      <c r="N16" s="45">
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="45">
         <f t="shared" si="0"/>
         <v>961214.28571428568</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="S16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q16" s="10">
+      <c r="T16" s="10">
         <v>1050000</v>
       </c>
-      <c r="R16" s="10"/>
+      <c r="U16" s="10"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
@@ -1825,17 +1897,20 @@
       <c r="K17" s="14"/>
       <c r="L17" s="14"/>
       <c r="M17" s="14"/>
-      <c r="N17" s="45">
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="45">
         <f t="shared" si="0"/>
         <v>1023750</v>
       </c>
-      <c r="P17" s="2" t="s">
+      <c r="S17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
@@ -1867,19 +1942,22 @@
       <c r="M18" s="14">
         <v>550000</v>
       </c>
-      <c r="N18" s="45">
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="45">
         <f t="shared" si="0"/>
         <v>540062.5</v>
       </c>
-      <c r="P18" s="2" t="s">
+      <c r="S18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q18" s="10">
+      <c r="T18" s="10">
         <v>675000</v>
       </c>
-      <c r="R18" s="10"/>
+      <c r="U18" s="10"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
@@ -1897,17 +1975,20 @@
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
       <c r="M19" s="14"/>
-      <c r="N19" s="45">
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="45">
         <f t="shared" si="0"/>
         <v>582750</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="S19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
@@ -1935,19 +2016,22 @@
         <v>636000</v>
       </c>
       <c r="M20" s="14"/>
-      <c r="N20" s="45">
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="45">
         <f t="shared" si="0"/>
         <v>631583.33333333337</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="S20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Q20" s="10">
+      <c r="T20" s="10">
         <v>713000</v>
       </c>
-      <c r="R20" s="10"/>
+      <c r="U20" s="10"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -1965,17 +2049,20 @@
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="14"/>
-      <c r="N21" s="45">
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="45">
         <f t="shared" si="0"/>
         <v>708750</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="S21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
@@ -2001,17 +2088,20 @@
         <v>225000</v>
       </c>
       <c r="M22" s="14"/>
-      <c r="N22" s="45">
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="45">
         <f t="shared" si="0"/>
         <v>200333.4</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="S22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="Q22" s="10">
+      <c r="T22" s="10">
         <v>240000</v>
       </c>
-      <c r="R22" s="10">
+      <c r="U22" s="10">
         <v>184017</v>
       </c>
     </row>
@@ -2148,6 +2238,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
+    <cfRule type="colorScale" priority="389">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="390">
       <colorScale>
         <cfvo type="min"/>
@@ -2158,18 +2258,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="389">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
+    <cfRule type="colorScale" priority="393">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="400">
       <colorScale>
         <cfvo type="min"/>
@@ -2180,18 +2280,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="393">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
+    <cfRule type="colorScale" priority="387">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="388">
       <colorScale>
         <cfvo type="min"/>
@@ -2202,18 +2302,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="387">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
+    <cfRule type="colorScale" priority="392">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="399">
       <colorScale>
         <cfvo type="min"/>
@@ -2224,29 +2324,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="392">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21">
+    <cfRule type="colorScale" priority="391">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="398">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="391">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2520,17 +2610,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20:K20">
+    <cfRule type="colorScale" priority="184">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="432">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="184">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2721,7 +2811,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9:M9">
+  <conditionalFormatting sqref="B9:P9">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -2733,7 +2823,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11:M11">
+  <conditionalFormatting sqref="B11:P11">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
@@ -2745,7 +2835,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:M13">
+  <conditionalFormatting sqref="B13:P13">
     <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
@@ -2757,7 +2847,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:M14">
+  <conditionalFormatting sqref="B14:P14">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
@@ -2769,7 +2859,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B18:M18">
+  <conditionalFormatting sqref="B18:P18">
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
@@ -2782,6 +2872,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
+    <cfRule type="colorScale" priority="260">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="278">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="296">
       <colorScale>
         <cfvo type="min"/>
@@ -2792,28 +2902,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="260">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="278">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
+    <cfRule type="colorScale" priority="259">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="277">
       <colorScale>
         <cfvo type="min"/>
@@ -2834,18 +2934,28 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="259">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
+    <cfRule type="colorScale" priority="258">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="276">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="294">
       <colorScale>
         <cfvo type="min"/>
@@ -2856,28 +2966,28 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="258">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="276">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
+    <cfRule type="colorScale" priority="257">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="275">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="293">
       <colorScale>
         <cfvo type="min"/>
@@ -2888,49 +2998,29 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="257">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="275">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
+    <cfRule type="colorScale" priority="256">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="274">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="292">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="256">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="274">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2952,17 +3042,17 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="273">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="291">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="273">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2984,6 +3074,16 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="272">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="290">
       <colorScale>
         <cfvo type="min"/>
@@ -2994,18 +3094,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="272">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
+    <cfRule type="colorScale" priority="253">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="271">
       <colorScale>
         <cfvo type="min"/>
@@ -3016,16 +3116,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="253">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="289">
       <colorScale>
         <cfvo type="min"/>
@@ -3038,6 +3128,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
+    <cfRule type="colorScale" priority="252">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="270">
       <colorScale>
         <cfvo type="min"/>
@@ -3048,16 +3148,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="252">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="288">
       <colorScale>
         <cfvo type="min"/>
@@ -3070,17 +3160,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
+    <cfRule type="colorScale" priority="251">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="269">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="251">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3176,6 +3266,16 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="266">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="284">
       <colorScale>
         <cfvo type="min"/>
@@ -3186,39 +3286,29 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="266">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18">
+    <cfRule type="colorScale" priority="247">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="265">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="283">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="265">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="247">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3294,6 +3384,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21">
+    <cfRule type="colorScale" priority="244">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="262">
       <colorScale>
         <cfvo type="min"/>
@@ -3314,39 +3414,29 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="244">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22">
+    <cfRule type="colorScale" priority="243">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="261">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="279">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="261">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="243">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3657,6 +3747,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D8 J8 F8 H8">
+    <cfRule type="colorScale" priority="329">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D8">
     <cfRule type="colorScale" priority="347">
       <colorScale>
@@ -3705,6 +3807,1036 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D12">
+    <cfRule type="colorScale" priority="343">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="colorScale" priority="342">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J14 D14 F14 H14">
+    <cfRule type="colorScale" priority="323">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="colorScale" priority="341">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="colorScale" priority="340">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J16 D16 F16 H16">
+    <cfRule type="colorScale" priority="321">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="colorScale" priority="339">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17">
+    <cfRule type="colorScale" priority="338">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="colorScale" priority="336">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21">
+    <cfRule type="colorScale" priority="334">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22 J22 F22 H22">
+    <cfRule type="colorScale" priority="315">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22">
+    <cfRule type="colorScale" priority="333">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:E18">
+    <cfRule type="colorScale" priority="337">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:E20">
+    <cfRule type="colorScale" priority="335">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:H18 J18">
+    <cfRule type="colorScale" priority="382">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:H20 J20">
+    <cfRule type="colorScale" priority="384">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5 F5 D5 H5">
+    <cfRule type="colorScale" priority="332">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6 F6 D6 H6">
+    <cfRule type="colorScale" priority="331">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7 J7 D7 H7">
+    <cfRule type="colorScale" priority="330">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9 J9 D9 H9">
+    <cfRule type="colorScale" priority="328">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10 J10 D10 H10">
+    <cfRule type="colorScale" priority="327">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13 J13 D13 H13">
+    <cfRule type="colorScale" priority="324">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:H5 D5 J5">
+    <cfRule type="colorScale" priority="369">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6:H6 D6 J6">
+    <cfRule type="colorScale" priority="370">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:H7 D7 J7">
+    <cfRule type="colorScale" priority="371">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:H8 D8 J8">
+    <cfRule type="colorScale" priority="372">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9:H9 D9 J9">
+    <cfRule type="colorScale" priority="373">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10:H10 D10 J10">
+    <cfRule type="colorScale" priority="374">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11:H11 D11 J11">
+    <cfRule type="colorScale" priority="375">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:H12 D12 J12">
+    <cfRule type="colorScale" priority="376">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13:H13 D13 J13">
+    <cfRule type="colorScale" priority="377">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:H14 D14 J14">
+    <cfRule type="colorScale" priority="378">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:H15 D15 J15">
+    <cfRule type="colorScale" priority="379">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16:H16 D16 J16">
+    <cfRule type="colorScale" priority="380">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:H17 D17 J17">
+    <cfRule type="colorScale" priority="381">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19:H19 D19 J19">
+    <cfRule type="colorScale" priority="383">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21:H21 D21 J21">
+    <cfRule type="colorScale" priority="385">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:H22 D22 J22">
+    <cfRule type="colorScale" priority="386">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="colorScale" priority="314">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="colorScale" priority="313">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="colorScale" priority="312">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="colorScale" priority="311">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9">
+    <cfRule type="colorScale" priority="310">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10">
+    <cfRule type="colorScale" priority="309">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="colorScale" priority="308">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
+    <cfRule type="colorScale" priority="307">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="colorScale" priority="306">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14">
+    <cfRule type="colorScale" priority="305">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
+    <cfRule type="colorScale" priority="304">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16">
+    <cfRule type="colorScale" priority="303">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
+    <cfRule type="colorScale" priority="302">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="colorScale" priority="301">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="colorScale" priority="300">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="colorScale" priority="299">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G21">
+    <cfRule type="colorScale" priority="298">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="colorScale" priority="297">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17 J17 D17 F17">
+    <cfRule type="colorScale" priority="320">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18 J18 D18:F18">
+    <cfRule type="colorScale" priority="319">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21 J21 D21 F21">
+    <cfRule type="colorScale" priority="316">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="colorScale" priority="211">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6">
+    <cfRule type="colorScale" priority="210">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
+    <cfRule type="colorScale" priority="198">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8">
+    <cfRule type="colorScale" priority="209">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I9">
+    <cfRule type="colorScale" priority="208">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I10">
+    <cfRule type="colorScale" priority="207">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11">
+    <cfRule type="colorScale" priority="206">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12">
+    <cfRule type="colorScale" priority="205">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13">
+    <cfRule type="colorScale" priority="204">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I14">
+    <cfRule type="colorScale" priority="203">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15">
+    <cfRule type="colorScale" priority="202">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16">
+    <cfRule type="colorScale" priority="201">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I17">
+    <cfRule type="colorScale" priority="200">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I18">
+    <cfRule type="colorScale" priority="193">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="199">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I19">
+    <cfRule type="colorScale" priority="196">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I20">
+    <cfRule type="colorScale" priority="197">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I21">
+    <cfRule type="colorScale" priority="195">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22">
+    <cfRule type="colorScale" priority="194">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5">
+    <cfRule type="colorScale" priority="368">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6">
+    <cfRule type="colorScale" priority="367">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="colorScale" priority="366">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J8">
+    <cfRule type="colorScale" priority="365">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J9">
+    <cfRule type="colorScale" priority="364">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J10">
+    <cfRule type="colorScale" priority="363">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11 J11 D11 H11">
+    <cfRule type="colorScale" priority="326">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J11">
+    <cfRule type="colorScale" priority="362">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D12 J12 F12 H12">
     <cfRule type="colorScale" priority="325">
       <colorScale>
@@ -3717,572 +4849,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D12">
-    <cfRule type="colorScale" priority="343">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D13">
-    <cfRule type="colorScale" priority="342">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D14">
-    <cfRule type="colorScale" priority="341">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="colorScale" priority="340">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D16">
-    <cfRule type="colorScale" priority="339">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17">
-    <cfRule type="colorScale" priority="338">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19">
-    <cfRule type="colorScale" priority="336">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D21">
-    <cfRule type="colorScale" priority="334">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D22">
-    <cfRule type="colorScale" priority="333">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:E18">
-    <cfRule type="colorScale" priority="337">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D20:E20">
-    <cfRule type="colorScale" priority="335">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:H18 J18">
-    <cfRule type="colorScale" priority="382">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D20:H20 J20">
-    <cfRule type="colorScale" priority="384">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11 J11 D11 H11">
-    <cfRule type="colorScale" priority="326">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:H5 D5 J5">
-    <cfRule type="colorScale" priority="369">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6:H6 D6 J6">
-    <cfRule type="colorScale" priority="370">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:H7 D7 J7">
-    <cfRule type="colorScale" priority="371">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:H8 D8 J8">
-    <cfRule type="colorScale" priority="372">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9:H9 D9 J9">
-    <cfRule type="colorScale" priority="373">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10:H10 D10 J10">
-    <cfRule type="colorScale" priority="374">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11:H11 D11 J11">
-    <cfRule type="colorScale" priority="375">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12:H12 D12 J12">
-    <cfRule type="colorScale" priority="376">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13:H13 D13 J13">
-    <cfRule type="colorScale" priority="377">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14:H14 D14 J14">
-    <cfRule type="colorScale" priority="378">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15:H15 D15 J15">
-    <cfRule type="colorScale" priority="379">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16:H16 D16 J16">
-    <cfRule type="colorScale" priority="380">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17:H17 D17 J17">
-    <cfRule type="colorScale" priority="381">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19:H19 D19 J19">
-    <cfRule type="colorScale" priority="383">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21:H21 D21 J21">
-    <cfRule type="colorScale" priority="385">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22:H22 D22 J22">
-    <cfRule type="colorScale" priority="386">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="colorScale" priority="314">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="colorScale" priority="313">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
-    <cfRule type="colorScale" priority="312">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="colorScale" priority="311">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G9">
-    <cfRule type="colorScale" priority="310">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G10">
-    <cfRule type="colorScale" priority="309">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="colorScale" priority="308">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="colorScale" priority="306">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G14">
-    <cfRule type="colorScale" priority="305">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
-    <cfRule type="colorScale" priority="304">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
-    <cfRule type="colorScale" priority="303">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17">
-    <cfRule type="colorScale" priority="302">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G18">
-    <cfRule type="colorScale" priority="301">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
-    <cfRule type="colorScale" priority="300">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G20">
-    <cfRule type="colorScale" priority="299">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G21">
-    <cfRule type="colorScale" priority="298">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22">
-    <cfRule type="colorScale" priority="297">
+  <conditionalFormatting sqref="J12">
+    <cfRule type="colorScale" priority="361">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J13">
+    <cfRule type="colorScale" priority="360">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J14">
+    <cfRule type="colorScale" priority="359">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4305,6 +4897,54 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J15">
+    <cfRule type="colorScale" priority="358">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J16">
+    <cfRule type="colorScale" priority="357">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J17">
+    <cfRule type="colorScale" priority="356">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J18">
+    <cfRule type="colorScale" priority="355">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H19 J19 D19 F19">
     <cfRule type="colorScale" priority="318">
       <colorScale>
@@ -4317,6 +4957,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J19">
+    <cfRule type="colorScale" priority="354">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H20 J20 D20:F20">
     <cfRule type="colorScale" priority="317">
       <colorScale>
@@ -4329,544 +4981,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5">
-    <cfRule type="colorScale" priority="211">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6">
-    <cfRule type="colorScale" priority="210">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="colorScale" priority="198">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I8">
-    <cfRule type="colorScale" priority="209">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I9">
-    <cfRule type="colorScale" priority="208">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I10">
-    <cfRule type="colorScale" priority="207">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11">
-    <cfRule type="colorScale" priority="206">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I12">
-    <cfRule type="colorScale" priority="205">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
-    <cfRule type="colorScale" priority="204">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I14">
-    <cfRule type="colorScale" priority="203">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I15">
-    <cfRule type="colorScale" priority="202">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I16">
-    <cfRule type="colorScale" priority="201">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I17">
-    <cfRule type="colorScale" priority="200">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I18">
-    <cfRule type="colorScale" priority="199">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="193">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I19">
-    <cfRule type="colorScale" priority="196">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I20">
-    <cfRule type="colorScale" priority="197">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I21">
-    <cfRule type="colorScale" priority="195">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22">
-    <cfRule type="colorScale" priority="194">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5 F5 D5 H5">
-    <cfRule type="colorScale" priority="332">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5">
-    <cfRule type="colorScale" priority="368">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6 F6 D6 H6">
-    <cfRule type="colorScale" priority="331">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6">
-    <cfRule type="colorScale" priority="367">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7 F7 D7 H7">
-    <cfRule type="colorScale" priority="330">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="colorScale" priority="366">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J8 D8 F8 H8">
-    <cfRule type="colorScale" priority="329">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J8">
-    <cfRule type="colorScale" priority="365">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J9 F9 D9 H9">
-    <cfRule type="colorScale" priority="328">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J9">
-    <cfRule type="colorScale" priority="364">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J10 F10 D10 H10">
-    <cfRule type="colorScale" priority="327">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J10">
-    <cfRule type="colorScale" priority="363">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J11">
-    <cfRule type="colorScale" priority="362">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J12">
-    <cfRule type="colorScale" priority="361">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J13 F13 D13 H13">
-    <cfRule type="colorScale" priority="324">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J13">
-    <cfRule type="colorScale" priority="360">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J14 D14 F14 H14">
-    <cfRule type="colorScale" priority="323">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J14">
-    <cfRule type="colorScale" priority="359">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J15">
-    <cfRule type="colorScale" priority="358">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J16 D16 F16 H16">
-    <cfRule type="colorScale" priority="321">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J16">
-    <cfRule type="colorScale" priority="357">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J17 H17 D17 F17">
-    <cfRule type="colorScale" priority="320">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J17">
-    <cfRule type="colorScale" priority="356">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J18 H18 D18:F18">
-    <cfRule type="colorScale" priority="319">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J18">
-    <cfRule type="colorScale" priority="355">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J19">
-    <cfRule type="colorScale" priority="354">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J20">
     <cfRule type="colorScale" priority="353">
       <colorScale>
@@ -4879,18 +4993,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J21 H21 D21 F21">
-    <cfRule type="colorScale" priority="316">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J21">
     <cfRule type="colorScale" priority="352">
       <colorScale>
@@ -4903,18 +5005,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J22 D22 F22 H22">
-    <cfRule type="colorScale" priority="315">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J22">
     <cfRule type="colorScale" priority="351">
       <colorScale>
@@ -5215,7 +5305,47 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M22">
+  <conditionalFormatting sqref="M5:P22">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
@@ -5226,48 +5356,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P6">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S6">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
@@ -5279,7 +5369,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P7">
+  <conditionalFormatting sqref="S7">
     <cfRule type="colorScale" priority="53">
       <colorScale>
         <cfvo type="min"/>
@@ -5291,7 +5381,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P8">
+  <conditionalFormatting sqref="S8">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="min"/>
@@ -5303,7 +5393,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P9">
+  <conditionalFormatting sqref="S9">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -5315,7 +5405,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P10">
+  <conditionalFormatting sqref="S10">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
@@ -5327,7 +5417,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P11">
+  <conditionalFormatting sqref="S11">
     <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
@@ -5339,7 +5429,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P12">
+  <conditionalFormatting sqref="S12">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
@@ -5351,7 +5441,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P13">
+  <conditionalFormatting sqref="S13">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
@@ -5362,18 +5462,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P14:P15">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S14:S15">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="47">
       <colorScale>
         <cfvo type="min"/>
@@ -5384,18 +5484,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P16">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S16">
     <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
@@ -5417,7 +5507,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P17">
+  <conditionalFormatting sqref="S17">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
@@ -5428,18 +5528,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="39">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P18">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S18">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
@@ -5450,18 +5550,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P19:P20">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S19:S20">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
@@ -5483,7 +5573,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P21">
+  <conditionalFormatting sqref="S21">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
@@ -5494,18 +5594,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="37">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P22">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S22">
     <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="min"/>
@@ -5517,7 +5607,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5">
+  <conditionalFormatting sqref="T5">
     <cfRule type="colorScale" priority="121">
       <colorScale>
         <cfvo type="min"/>
@@ -5529,7 +5619,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q6">
+  <conditionalFormatting sqref="T6">
     <cfRule type="colorScale" priority="120">
       <colorScale>
         <cfvo type="min"/>
@@ -5541,7 +5631,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q7">
+  <conditionalFormatting sqref="T7">
     <cfRule type="colorScale" priority="119">
       <colorScale>
         <cfvo type="min"/>
@@ -5553,7 +5643,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q8">
+  <conditionalFormatting sqref="T8">
     <cfRule type="colorScale" priority="118">
       <colorScale>
         <cfvo type="min"/>
@@ -5565,7 +5655,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q9">
+  <conditionalFormatting sqref="T9">
     <cfRule type="colorScale" priority="117">
       <colorScale>
         <cfvo type="min"/>
@@ -5577,7 +5667,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q10">
+  <conditionalFormatting sqref="T10">
     <cfRule type="colorScale" priority="116">
       <colorScale>
         <cfvo type="min"/>
@@ -5589,7 +5679,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q11">
+  <conditionalFormatting sqref="T11">
     <cfRule type="colorScale" priority="115">
       <colorScale>
         <cfvo type="min"/>
@@ -5601,7 +5691,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q12">
+  <conditionalFormatting sqref="T12">
     <cfRule type="colorScale" priority="114">
       <colorScale>
         <cfvo type="min"/>
@@ -5613,7 +5703,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q13">
+  <conditionalFormatting sqref="T13">
     <cfRule type="colorScale" priority="113">
       <colorScale>
         <cfvo type="min"/>
@@ -5625,7 +5715,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q14">
+  <conditionalFormatting sqref="T14">
     <cfRule type="colorScale" priority="112">
       <colorScale>
         <cfvo type="min"/>
@@ -5637,7 +5727,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q15">
+  <conditionalFormatting sqref="T15">
     <cfRule type="colorScale" priority="111">
       <colorScale>
         <cfvo type="min"/>
@@ -5649,7 +5739,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q16">
+  <conditionalFormatting sqref="T16">
     <cfRule type="colorScale" priority="110">
       <colorScale>
         <cfvo type="min"/>
@@ -5661,7 +5751,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q17">
+  <conditionalFormatting sqref="T17">
     <cfRule type="colorScale" priority="109">
       <colorScale>
         <cfvo type="min"/>
@@ -5673,7 +5763,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q18">
+  <conditionalFormatting sqref="T18">
     <cfRule type="colorScale" priority="108">
       <colorScale>
         <cfvo type="min"/>
@@ -5685,7 +5775,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q19">
+  <conditionalFormatting sqref="T19">
     <cfRule type="colorScale" priority="107">
       <colorScale>
         <cfvo type="min"/>
@@ -5697,7 +5787,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q20">
+  <conditionalFormatting sqref="T20">
     <cfRule type="colorScale" priority="106">
       <colorScale>
         <cfvo type="min"/>
@@ -5709,7 +5799,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q21">
+  <conditionalFormatting sqref="T21">
     <cfRule type="colorScale" priority="105">
       <colorScale>
         <cfvo type="min"/>
@@ -5721,7 +5811,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q22">
+  <conditionalFormatting sqref="T22">
     <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="min"/>
@@ -5733,7 +5823,57 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:R5">
+  <conditionalFormatting sqref="T5:U5">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="103">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="122">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="141">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="164">
       <colorScale>
         <cfvo type="min"/>
@@ -5744,58 +5884,38 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="122">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="72">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="141">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="67">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="103">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q6:R6">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T6:U6">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="102">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="123">
       <colorScale>
         <cfvo type="min"/>
@@ -5806,6 +5926,16 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="142">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="165">
       <colorScale>
         <cfvo type="min"/>
@@ -5816,48 +5946,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="102">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="71">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="142">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="66">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q7:R7">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T7:U7">
     <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
@@ -5868,6 +5958,26 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="101">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="124">
       <colorScale>
         <cfvo type="min"/>
@@ -5878,6 +5988,16 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="143">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="166">
       <colorScale>
         <cfvo type="min"/>
@@ -5888,38 +6008,38 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="101">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="143">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q8:R8">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:U8">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="100">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="125">
       <colorScale>
         <cfvo type="min"/>
@@ -5940,16 +6060,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="100">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="167">
       <colorScale>
         <cfvo type="min"/>
@@ -5960,28 +6070,38 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="69">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q9:R9">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T9:U9">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="99">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="126">
       <colorScale>
         <cfvo type="min"/>
@@ -5992,17 +6112,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="63">
+    <cfRule type="colorScale" priority="145">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6022,28 +6132,48 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="145">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="99">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q10:R10">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T10:U10">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="85">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="98">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="127">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="146">
       <colorScale>
         <cfvo type="min"/>
@@ -6054,48 +6184,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="127">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="98">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="85">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:R11">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T11:U11">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
@@ -6106,6 +6206,16 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="97">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="128">
       <colorScale>
         <cfvo type="min"/>
@@ -6116,26 +6226,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="61">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="97">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="147">
       <colorScale>
         <cfvo type="min"/>
@@ -6147,7 +6237,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q12:R12">
+  <conditionalFormatting sqref="T12:U12">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="83">
       <colorScale>
         <cfvo type="min"/>
@@ -6178,16 +6278,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="148">
       <colorScale>
         <cfvo type="min"/>
@@ -6199,7 +6289,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q13:R13">
+  <conditionalFormatting sqref="T13:U13">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -6220,6 +6320,26 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="130">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="149">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="159">
       <colorScale>
         <cfvo type="min"/>
@@ -6230,38 +6350,48 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="130">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="59">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="149">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q14:R14">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T14:U14">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="81">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="94">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="131">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="150">
       <colorScale>
         <cfvo type="min"/>
@@ -6272,46 +6402,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="81">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="94">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="131">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="160">
       <colorScale>
         <cfvo type="min"/>
@@ -6323,7 +6413,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q15:R15">
+  <conditionalFormatting sqref="T15:U15">
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="93">
       <colorScale>
         <cfvo type="min"/>
@@ -6364,18 +6464,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="80">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q16:R16">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T16:U16">
     <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="min"/>
@@ -6386,6 +6476,46 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="79">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="133">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="152">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="161">
       <colorScale>
         <cfvo type="min"/>
@@ -6396,48 +6526,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="92">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="79">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="133">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="152">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q17:R17">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T17:U17">
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
@@ -6448,16 +6548,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="134">
       <colorScale>
         <cfvo type="min"/>
@@ -6479,7 +6569,57 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q18:R18">
+  <conditionalFormatting sqref="T18:U18">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="77">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="135">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="154">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="162">
       <colorScale>
         <cfvo type="min"/>
@@ -6490,58 +6630,18 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="90">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="135">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="154">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="77">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q19:R19">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T19:U19">
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="89">
       <colorScale>
         <cfvo type="min"/>
@@ -6572,18 +6672,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q20:R20">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T20:U20">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
@@ -6594,6 +6684,26 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="137">
       <colorScale>
         <cfvo type="min"/>
@@ -6614,16 +6724,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="163">
       <colorScale>
         <cfvo type="min"/>
@@ -6634,18 +6734,28 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="88">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q21:R21">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T21:U21">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="87">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="138">
       <colorScale>
         <cfvo type="min"/>
@@ -6666,28 +6776,28 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="87">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q22:R22">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T22:U22">
+    <cfRule type="colorScale" priority="73">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="139">
       <colorScale>
         <cfvo type="min"/>
@@ -6699,26 +6809,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="158">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="73">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="86">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8077,17 +8167,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8111,6 +8201,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
@@ -8121,29 +8221,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8297,6 +8387,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
@@ -8307,29 +8407,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A34">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8449,17 +8539,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8483,6 +8573,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -8493,29 +8593,19 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
